--- a/data/trans_orig/Q4502_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137618</t>
+          <t>137598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183013</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129245</t>
+          <t>129398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172532</t>
+          <t>172030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>276110</t>
+          <t>279573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338604</t>
+          <t>340881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164959</t>
+          <t>163221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213597</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>119807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160539</t>
+          <t>161292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>299068</t>
+          <t>295107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358512</t>
+          <t>359159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178211</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226277</t>
+          <t>226160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>212009</t>
+          <t>207733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>261873</t>
+          <t>259196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>404645</t>
+          <t>399811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>472148</t>
+          <t>469660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53200</t>
+          <t>51659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45759</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73695</t>
+          <t>73275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106736</t>
+          <t>106437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146665</t>
+          <t>146996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105286</t>
+          <t>105133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>145926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>220824</t>
+          <t>222874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>277508</t>
+          <t>278704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179606</t>
+          <t>181057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231595</t>
+          <t>234537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156282</t>
+          <t>154754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207696</t>
+          <t>205819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348960</t>
+          <t>347631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>423380</t>
+          <t>423535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184354</t>
+          <t>182445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238701</t>
+          <t>237483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137702</t>
+          <t>138268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186865</t>
+          <t>185619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334908</t>
+          <t>336328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>404635</t>
+          <t>410384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>280814</t>
+          <t>282173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339266</t>
+          <t>340448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>286569</t>
+          <t>287560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345384</t>
+          <t>347033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>585010</t>
+          <t>583995</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>670616</t>
+          <t>673479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38778</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67782</t>
+          <t>68409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56013</t>
+          <t>53525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87144</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101998</t>
+          <t>102022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146563</t>
+          <t>143404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159003</t>
+          <t>159853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210690</t>
+          <t>208379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209641</t>
+          <t>212044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265367</t>
+          <t>264229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384156</t>
+          <t>383098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>455940</t>
+          <t>458252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139558</t>
+          <t>139763</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184164</t>
+          <t>185807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152876</t>
+          <t>149142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196786</t>
+          <t>194524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304651</t>
+          <t>303903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366209</t>
+          <t>369588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>115225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157833</t>
+          <t>156908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100931</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139869</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224475</t>
+          <t>226579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283986</t>
+          <t>284850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176507</t>
+          <t>173257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>222175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145269</t>
+          <t>144673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190259</t>
+          <t>191287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334349</t>
+          <t>332694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>399783</t>
+          <t>398217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>53762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35240</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70343</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105460</t>
+          <t>108023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123736</t>
+          <t>123364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168353</t>
+          <t>167184</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153610</t>
+          <t>154407</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198003</t>
+          <t>198265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282777</t>
+          <t>287872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>349851</t>
+          <t>354264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>169661</t>
+          <t>170994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217488</t>
+          <t>218745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153365</t>
+          <t>154488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200121</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332988</t>
+          <t>336164</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>403603</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194051</t>
+          <t>192745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244036</t>
+          <t>244789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168893</t>
+          <t>169880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>219557</t>
+          <t>221939</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>374447</t>
+          <t>375460</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>446820</t>
+          <t>446881</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230691</t>
+          <t>231832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283864</t>
+          <t>285644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>246185</t>
+          <t>244066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>304826</t>
+          <t>301856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>489398</t>
+          <t>490492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>567522</t>
+          <t>567234</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70445</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103520</t>
+          <t>103297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122419</t>
+          <t>121692</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160053</t>
+          <t>160193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212563</t>
+          <t>212048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167687</t>
+          <t>166500</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215820</t>
+          <t>215628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264938</t>
+          <t>265843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321808</t>
+          <t>322844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>449763</t>
+          <t>446122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>523226</t>
+          <t>520991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>668751</t>
+          <t>671434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>769891</t>
+          <t>767657</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>632389</t>
+          <t>634255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>725137</t>
+          <t>731378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1336445</t>
+          <t>1330014</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1466128</t>
+          <t>1460295</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>700889</t>
+          <t>702665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>797745</t>
+          <t>803949</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>570474</t>
+          <t>575402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>656808</t>
+          <t>666360</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1297411</t>
+          <t>1300068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1430888</t>
+          <t>1431197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>913899</t>
+          <t>913761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1022106</t>
+          <t>1020629</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>939944</t>
+          <t>929846</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1048297</t>
+          <t>1043322</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1882771</t>
+          <t>1888742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2037094</t>
+          <t>2037541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168499</t>
+          <t>168536</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>224723</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>227976</t>
+          <t>229760</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>292760</t>
+          <t>288571</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>414695</t>
+          <t>411947</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>495749</t>
+          <t>493046</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>594178</t>
+          <t>592539</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>686520</t>
+          <t>683628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>780637</t>
+          <t>775347</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>879963</t>
+          <t>876210</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,47 +3962,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1471670</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1402924</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1538111</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>22,14%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>23,14%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1471670</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>1406372</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1535282</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>260606</t>
+          <t>261517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>315876</t>
+          <t>315444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>239489</t>
+          <t>237957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291947</t>
+          <t>289711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>516234</t>
+          <t>514288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589546</t>
+          <t>592956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158489</t>
+          <t>159022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203793</t>
+          <t>207472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140377</t>
+          <t>141102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185219</t>
+          <t>184180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>312624</t>
+          <t>312029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>380396</t>
+          <t>374688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72756</t>
+          <t>72608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107829</t>
+          <t>106988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125767</t>
+          <t>123733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165697</t>
+          <t>169422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>220587</t>
+          <t>221294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38927</t>
+          <t>39725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>70359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95879</t>
+          <t>94959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136309</t>
+          <t>135377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117108</t>
+          <t>116322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162750</t>
+          <t>158939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226556</t>
+          <t>224091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284824</t>
+          <t>285634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389922</t>
+          <t>389223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>455965</t>
+          <t>452665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>366088</t>
+          <t>362484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>428565</t>
+          <t>430078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>773966</t>
+          <t>772448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>865587</t>
+          <t>858907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182386</t>
+          <t>181939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>235368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155831</t>
+          <t>158581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>205570</t>
+          <t>208385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350514</t>
+          <t>351170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>425981</t>
+          <t>428577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139914</t>
+          <t>135809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>183903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144441</t>
+          <t>143763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196087</t>
+          <t>197287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296106</t>
+          <t>296280</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364504</t>
+          <t>363398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64027</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47351</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79139</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91288</t>
+          <t>91851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133634</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154373</t>
+          <t>156225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205650</t>
+          <t>207947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192617</t>
+          <t>190878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247669</t>
+          <t>245436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>359087</t>
+          <t>361284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>437203</t>
+          <t>435028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213147</t>
+          <t>214288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268890</t>
+          <t>269074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221484</t>
+          <t>221609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>278344</t>
+          <t>275352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450705</t>
+          <t>455012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>528329</t>
+          <t>529156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140795</t>
+          <t>142039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187607</t>
+          <t>187501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100742</t>
+          <t>99625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>143730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254551</t>
+          <t>254069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>317970</t>
+          <t>319620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143965</t>
+          <t>148013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192778</t>
+          <t>193512</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139856</t>
+          <t>138324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>184301</t>
+          <t>186132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298883</t>
+          <t>297588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>365251</t>
+          <t>366300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>24083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77732</t>
+          <t>78751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76886</t>
+          <t>76020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118467</t>
+          <t>115804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124925</t>
+          <t>125499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173427</t>
+          <t>171210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159726</t>
+          <t>160037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209857</t>
+          <t>209974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297263</t>
+          <t>296408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>364741</t>
+          <t>363741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>372187</t>
+          <t>373253</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433006</t>
+          <t>435669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>432550</t>
+          <t>433235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>500176</t>
+          <t>496647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>822650</t>
+          <t>822623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>914047</t>
+          <t>911312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164986</t>
+          <t>164084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212651</t>
+          <t>213590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154959</t>
+          <t>156694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202868</t>
+          <t>204688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>334108</t>
+          <t>333584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>404099</t>
+          <t>403739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146044</t>
+          <t>145847</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>194320</t>
+          <t>195247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>118473</t>
+          <t>121118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162508</t>
+          <t>165246</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276469</t>
+          <t>277759</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>345889</t>
+          <t>344434</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,82 +6774,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>78149</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>61728</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>95701</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>122022</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>102807</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>145305</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>78149</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>61466</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>96789</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>122022</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>101698</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>144040</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122757</t>
+          <t>122334</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171347</t>
+          <t>166366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>163210</t>
+          <t>161449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214125</t>
+          <t>214220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>301355</t>
+          <t>299200</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>368512</t>
+          <t>369204</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1292359</t>
+          <t>1294491</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1415937</t>
+          <t>1418662</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1315668</t>
+          <t>1323376</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1442570</t>
+          <t>1442045</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2647994</t>
+          <t>2645693</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2806750</t>
+          <t>2809654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>690908</t>
+          <t>689119</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>792078</t>
+          <t>787238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>593510</t>
+          <t>595189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>688115</t>
+          <t>691156</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1321056</t>
+          <t>1320565</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1457070</t>
+          <t>1461961</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>543861</t>
+          <t>545302</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>634688</t>
+          <t>634323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>533624</t>
+          <t>530137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>624752</t>
+          <t>623081</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1104330</t>
+          <t>1102663</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1228211</t>
+          <t>1230356</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>133688</t>
+          <t>129524</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>181814</t>
+          <t>180083</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>200578</t>
+          <t>197616</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>261439</t>
+          <t>258332</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>344448</t>
+          <t>344277</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>422226</t>
+          <t>420366</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>537442</t>
+          <t>540408</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>633271</t>
+          <t>629954</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>676338</t>
+          <t>675615</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>776322</t>
+          <t>776298</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1240922</t>
+          <t>1245479</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1375930</t>
+          <t>1388334</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron camiseta para protegerse del sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>165979</t>
+          <t>164618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212181</t>
+          <t>210118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156584</t>
+          <t>156945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>205144</t>
+          <t>203375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>332691</t>
+          <t>334369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398540</t>
+          <t>403187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182102</t>
+          <t>182914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230591</t>
+          <t>229857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158885</t>
+          <t>159001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206947</t>
+          <t>204503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>353297</t>
+          <t>351424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420906</t>
+          <t>419286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119818</t>
+          <t>119952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161913</t>
+          <t>163093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>115952</t>
+          <t>116796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155756</t>
+          <t>156133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>247190</t>
+          <t>245422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309467</t>
+          <t>308033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39534</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>53762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85481</t>
+          <t>85436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93695</t>
+          <t>93606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>132370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116440</t>
+          <t>116366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157106</t>
+          <t>159263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221216</t>
+          <t>219005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281969</t>
+          <t>279202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236487</t>
+          <t>233747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293193</t>
+          <t>292644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>237299</t>
+          <t>231568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>298654</t>
+          <t>292183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>486682</t>
+          <t>484775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>568790</t>
+          <t>566015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309057</t>
+          <t>311189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372339</t>
+          <t>369831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277023</t>
+          <t>275831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336587</t>
+          <t>338590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604246</t>
+          <t>611404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692800</t>
+          <t>695126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205435</t>
+          <t>208738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>264865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>216353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>267279</t>
+          <t>270802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>438469</t>
+          <t>432768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>512544</t>
+          <t>510565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42508</t>
+          <t>41744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72442</t>
+          <t>70140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54301</t>
+          <t>55203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76820</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118683</t>
+          <t>118693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>103455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146796</t>
+          <t>149920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163927</t>
+          <t>163526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214532</t>
+          <t>213374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281169</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348167</t>
+          <t>347606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145775</t>
+          <t>146224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194727</t>
+          <t>194126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>154685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201843</t>
+          <t>204048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>315368</t>
+          <t>312252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>381244</t>
+          <t>378386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>281868</t>
+          <t>280944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338692</t>
+          <t>334571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316949</t>
+          <t>313092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371196</t>
+          <t>368823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>607442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>689202</t>
+          <t>688308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157333</t>
+          <t>159046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>205533</t>
+          <t>210724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129378</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>174416</t>
+          <t>175387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>299880</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>367176</t>
+          <t>366990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>51131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>57901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64509</t>
+          <t>63246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99771</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42610</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73556</t>
+          <t>74591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>49740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83093</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>123403</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>100894</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>148824</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>123403</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>102985</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>146048</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188021</t>
+          <t>184780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236773</t>
+          <t>234570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187744</t>
+          <t>189686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243427</t>
+          <t>241674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390167</t>
+          <t>386713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>465266</t>
+          <t>467261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>218468</t>
+          <t>217821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270720</t>
+          <t>271493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207630</t>
+          <t>209468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263133</t>
+          <t>263747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>443884</t>
+          <t>438904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519000</t>
+          <t>520615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191375</t>
+          <t>192174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243995</t>
+          <t>242863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150020</t>
+          <t>148935</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198300</t>
+          <t>200421</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>354874</t>
+          <t>351089</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>427461</t>
+          <t>424902</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53823</t>
+          <t>54309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85556</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83725</t>
+          <t>84659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125042</t>
+          <t>123116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144817</t>
+          <t>145614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195149</t>
+          <t>198610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172968</t>
+          <t>175140</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>221665</t>
+          <t>224226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>284809</t>
+          <t>287049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>343598</t>
+          <t>344560</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>470326</t>
+          <t>471950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>552504</t>
+          <t>552627</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>779359</t>
+          <t>773715</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>878016</t>
+          <t>880910</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>784192</t>
+          <t>789039</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>883956</t>
+          <t>892658</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1589174</t>
+          <t>1595066</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1743024</t>
+          <t>1735133</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1042490</t>
+          <t>1044488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1153436</t>
+          <t>1151754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015155</t>
+          <t>1010943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1120226</t>
+          <t>1124122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2085915</t>
+          <t>2085510</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2246301</t>
+          <t>2240618</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>724365</t>
+          <t>723319</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>821776</t>
+          <t>822479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>652864</t>
+          <t>653481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>749805</t>
+          <t>745058</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1409084</t>
+          <t>1404719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1546482</t>
+          <t>1543192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>163769</t>
+          <t>163522</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>215427</t>
+          <t>216897</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>199520</t>
+          <t>195564</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>258114</t>
+          <t>257350</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>377967</t>
+          <t>377541</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>455164</t>
+          <t>459907</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>454455</t>
+          <t>450556</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>538886</t>
+          <t>533829</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>650015</t>
+          <t>653913</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>757022</t>
+          <t>753874</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1131405</t>
+          <t>1129156</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1264733</t>
+          <t>1259303</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4502_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4502_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137598</t>
+          <t>136992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>180280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129398</t>
+          <t>130736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172030</t>
+          <t>171217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>279573</t>
+          <t>280373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>340881</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163221</t>
+          <t>165661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212753</t>
+          <t>212980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119807</t>
+          <t>120334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>162869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295107</t>
+          <t>295974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359159</t>
+          <t>358172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175947</t>
+          <t>177984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226160</t>
+          <t>226348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207733</t>
+          <t>211663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>259196</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>399811</t>
+          <t>404404</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>469660</t>
+          <t>471189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51659</t>
+          <t>50125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44811</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73275</t>
+          <t>73691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106437</t>
+          <t>106456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146996</t>
+          <t>147047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105133</t>
+          <t>105017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145926</t>
+          <t>144759</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222874</t>
+          <t>221209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278704</t>
+          <t>281460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181057</t>
+          <t>180484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>234537</t>
+          <t>233797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154754</t>
+          <t>156343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205819</t>
+          <t>206551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>350338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>423535</t>
+          <t>425628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182445</t>
+          <t>184571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237483</t>
+          <t>238467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138268</t>
+          <t>136112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185619</t>
+          <t>184081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>336328</t>
+          <t>337120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>410384</t>
+          <t>409043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282173</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>340448</t>
+          <t>341497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>287560</t>
+          <t>285243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347033</t>
+          <t>347636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>583995</t>
+          <t>583409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>673479</t>
+          <t>668176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>39273</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68409</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87068</t>
+          <t>88935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102022</t>
+          <t>102957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143404</t>
+          <t>145413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159853</t>
+          <t>159292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208379</t>
+          <t>209873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,47 +1881,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>237161</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>209362</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>261181</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>237161</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>212044</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>264229</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383098</t>
+          <t>381204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458252</t>
+          <t>456151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139763</t>
+          <t>140229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185807</t>
+          <t>184139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149142</t>
+          <t>151559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194524</t>
+          <t>194831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303903</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369588</t>
+          <t>367593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115225</t>
+          <t>113450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156908</t>
+          <t>157171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139455</t>
+          <t>139755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226579</t>
+          <t>226186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284850</t>
+          <t>282945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173257</t>
+          <t>176934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222175</t>
+          <t>224805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144673</t>
+          <t>144819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191287</t>
+          <t>188417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332694</t>
+          <t>334429</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>398217</t>
+          <t>401441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27760</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61963</t>
+          <t>61187</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70189</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108023</t>
+          <t>105235</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>122026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167184</t>
+          <t>165843</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154407</t>
+          <t>156608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>198265</t>
+          <t>198136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287872</t>
+          <t>288423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354264</t>
+          <t>355443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170994</t>
+          <t>168317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218745</t>
+          <t>217928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154488</t>
+          <t>151768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204352</t>
+          <t>201534</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336164</t>
+          <t>331006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404455</t>
+          <t>405990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192745</t>
+          <t>191746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244789</t>
+          <t>241345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169880</t>
+          <t>169143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>221939</t>
+          <t>220940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>375460</t>
+          <t>378286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>446881</t>
+          <t>449564</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231832</t>
+          <t>231225</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285644</t>
+          <t>287444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244066</t>
+          <t>245748</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301856</t>
+          <t>303392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>490492</t>
+          <t>491404</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>567234</t>
+          <t>571100</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68609</t>
+          <t>68692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>102294</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82680</t>
+          <t>85241</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121692</t>
+          <t>123711</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160193</t>
+          <t>160509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212048</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166500</t>
+          <t>165634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>215628</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>265843</t>
+          <t>266625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>324854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>446122</t>
+          <t>443398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>520991</t>
+          <t>522656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>671434</t>
+          <t>670653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>767657</t>
+          <t>770502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>634255</t>
+          <t>634543</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>731378</t>
+          <t>729963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1330014</t>
+          <t>1335223</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1460295</t>
+          <t>1465103</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>702665</t>
+          <t>704526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>803949</t>
+          <t>803543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>575402</t>
+          <t>570063</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>666360</t>
+          <t>661976</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1300068</t>
+          <t>1299314</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1431197</t>
+          <t>1433515</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>913761</t>
+          <t>915692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1020629</t>
+          <t>1019740</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>929846</t>
+          <t>935491</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1043322</t>
+          <t>1044573</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1888742</t>
+          <t>1884962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2037541</t>
+          <t>2037002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168536</t>
+          <t>168925</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>222029</t>
+          <t>222485</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>229760</t>
+          <t>226090</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>287801</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>411947</t>
+          <t>412587</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>493046</t>
+          <t>494237</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>592539</t>
+          <t>595817</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>683628</t>
+          <t>690060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>775347</t>
+          <t>781416</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>876210</t>
+          <t>881237</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1402924</t>
+          <t>1404509</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1538111</t>
+          <t>1542174</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>261517</t>
+          <t>259784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>315444</t>
+          <t>314150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237957</t>
+          <t>240046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289711</t>
+          <t>292988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>514288</t>
+          <t>515997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>592956</t>
+          <t>590895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159022</t>
+          <t>158134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207472</t>
+          <t>205612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141102</t>
+          <t>137634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184180</t>
+          <t>184429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>312029</t>
+          <t>313304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374688</t>
+          <t>377058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72608</t>
+          <t>72387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106988</t>
+          <t>109222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85376</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123733</t>
+          <t>125414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>169422</t>
+          <t>169212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>221294</t>
+          <t>220413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39725</t>
+          <t>39899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>39124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70359</t>
+          <t>73356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94959</t>
+          <t>95212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>135377</t>
+          <t>136436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116322</t>
+          <t>117239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158939</t>
+          <t>160364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224091</t>
+          <t>225687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285634</t>
+          <t>284912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389223</t>
+          <t>385609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>452665</t>
+          <t>453414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>362484</t>
+          <t>365116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>430078</t>
+          <t>430797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>772448</t>
+          <t>773326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>858907</t>
+          <t>860414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181939</t>
+          <t>180625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235368</t>
+          <t>234673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158581</t>
+          <t>156694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208385</t>
+          <t>205449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351170</t>
+          <t>350393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>428577</t>
+          <t>424622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135809</t>
+          <t>139128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183903</t>
+          <t>190003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143763</t>
+          <t>146306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>197287</t>
+          <t>193505</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>296280</t>
+          <t>296954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363398</t>
+          <t>366779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>34935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66314</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>46921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81243</t>
+          <t>79066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135234</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156225</t>
+          <t>154917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207947</t>
+          <t>206636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190878</t>
+          <t>191847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245436</t>
+          <t>245650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361284</t>
+          <t>359074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435028</t>
+          <t>429799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>214288</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269074</t>
+          <t>267898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221609</t>
+          <t>220112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>275352</t>
+          <t>273657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>455012</t>
+          <t>454940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>529156</t>
+          <t>529414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142039</t>
+          <t>141646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187501</t>
+          <t>189931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99625</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143730</t>
+          <t>142941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254069</t>
+          <t>252910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>319620</t>
+          <t>318436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148013</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193512</t>
+          <t>194961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138324</t>
+          <t>138783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186132</t>
+          <t>185249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297588</t>
+          <t>295421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>366300</t>
+          <t>367073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78751</t>
+          <t>77130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76020</t>
+          <t>77141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115804</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125499</t>
+          <t>126978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171210</t>
+          <t>174106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160037</t>
+          <t>159268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209974</t>
+          <t>210674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296408</t>
+          <t>298495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>363741</t>
+          <t>367319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>373253</t>
+          <t>374134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>435669</t>
+          <t>438345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>431367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>496647</t>
+          <t>496162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>822623</t>
+          <t>824097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911312</t>
+          <t>912346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164084</t>
+          <t>163721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>213590</t>
+          <t>214613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>156694</t>
+          <t>156804</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204688</t>
+          <t>208336</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>333584</t>
+          <t>332729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403739</t>
+          <t>402978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>145847</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>195247</t>
+          <t>192648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121118</t>
+          <t>119321</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>165246</t>
+          <t>164627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277759</t>
+          <t>275707</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>344434</t>
+          <t>342682</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>57597</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61728</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95701</t>
+          <t>96324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102807</t>
+          <t>101251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145305</t>
+          <t>145883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122334</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>166366</t>
+          <t>167422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161449</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214220</t>
+          <t>214134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>299200</t>
+          <t>296652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>369204</t>
+          <t>366301</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1294491</t>
+          <t>1293931</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1418662</t>
+          <t>1409219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1323376</t>
+          <t>1318436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1442045</t>
+          <t>1435036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2645693</t>
+          <t>2648270</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2809654</t>
+          <t>2815526</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>689119</t>
+          <t>692270</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>787238</t>
+          <t>798143</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>595189</t>
+          <t>593993</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>691156</t>
+          <t>693284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1320565</t>
+          <t>1315986</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1445578</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>545302</t>
+          <t>546342</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>634323</t>
+          <t>636099</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>530137</t>
+          <t>532278</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>623081</t>
+          <t>624861</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1102663</t>
+          <t>1099410</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1230356</t>
+          <t>1234387</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>129524</t>
+          <t>128702</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>180083</t>
+          <t>180642</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>197616</t>
+          <t>200079</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>258332</t>
+          <t>262823</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>344277</t>
+          <t>345609</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>420366</t>
+          <t>422532</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>540408</t>
+          <t>542268</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>629954</t>
+          <t>630624</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>675615</t>
+          <t>675693</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>776298</t>
+          <t>775473</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1245479</t>
+          <t>1242505</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1388334</t>
+          <t>1374536</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164618</t>
+          <t>164431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210118</t>
+          <t>211874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156945</t>
+          <t>157109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>203375</t>
+          <t>203228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>334369</t>
+          <t>332994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403187</t>
+          <t>400058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182914</t>
+          <t>180899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229857</t>
+          <t>230771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159001</t>
+          <t>158583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204503</t>
+          <t>204024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>351424</t>
+          <t>354376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419286</t>
+          <t>421505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>119829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163093</t>
+          <t>162928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116796</t>
+          <t>115836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156133</t>
+          <t>155905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245422</t>
+          <t>249082</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308033</t>
+          <t>307003</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>40096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28009</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51527</t>
+          <t>50748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>53125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93606</t>
+          <t>92293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132370</t>
+          <t>131966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116366</t>
+          <t>114450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159263</t>
+          <t>156739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219005</t>
+          <t>217997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>279202</t>
+          <t>277522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>233747</t>
+          <t>233720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292644</t>
+          <t>292677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231568</t>
+          <t>236100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292183</t>
+          <t>292320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484775</t>
+          <t>483461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566015</t>
+          <t>566445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311189</t>
+          <t>310545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>369831</t>
+          <t>370467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275831</t>
+          <t>278710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338590</t>
+          <t>339355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611404</t>
+          <t>606490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>695126</t>
+          <t>696953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>207659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>264865</t>
+          <t>260058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216353</t>
+          <t>213568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>270802</t>
+          <t>269185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432768</t>
+          <t>438103</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>517338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>73685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>54887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>77938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118693</t>
+          <t>119205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>101733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149920</t>
+          <t>146178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163526</t>
+          <t>164835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213374</t>
+          <t>215383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281266</t>
+          <t>279291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347606</t>
+          <t>348486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146224</t>
+          <t>147236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194126</t>
+          <t>194138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154685</t>
+          <t>155162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204048</t>
+          <t>201734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312252</t>
+          <t>316398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>378386</t>
+          <t>380936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280944</t>
+          <t>278789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334571</t>
+          <t>336058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313092</t>
+          <t>315217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368823</t>
+          <t>369921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>607442</t>
+          <t>612920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688308</t>
+          <t>692971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>159046</t>
+          <t>158119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210724</t>
+          <t>206446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>130210</t>
+          <t>129150</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>175387</t>
+          <t>173189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>301283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>366990</t>
+          <t>369683</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51131</t>
+          <t>51040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57901</t>
+          <t>58286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63246</t>
+          <t>63798</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>99846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74591</t>
+          <t>74749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49740</t>
+          <t>50965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>81766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100894</t>
+          <t>103825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148824</t>
+          <t>146319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>184780</t>
+          <t>186693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234570</t>
+          <t>237951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189686</t>
+          <t>188754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241674</t>
+          <t>244869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386713</t>
+          <t>387267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>467261</t>
+          <t>463914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217821</t>
+          <t>215919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271493</t>
+          <t>270039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>209468</t>
+          <t>208453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>264695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>438904</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>520615</t>
+          <t>518986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192174</t>
+          <t>192400</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242863</t>
+          <t>242477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>148935</t>
+          <t>149884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200421</t>
+          <t>200769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>351089</t>
+          <t>355680</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>424902</t>
+          <t>429246</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54309</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85949</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>85462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123116</t>
+          <t>122587</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145614</t>
+          <t>146956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198610</t>
+          <t>197787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175140</t>
+          <t>173627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>224226</t>
+          <t>222855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>287049</t>
+          <t>282508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>344560</t>
+          <t>344350</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>471950</t>
+          <t>473445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>552627</t>
+          <t>552865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>773715</t>
+          <t>773392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>880910</t>
+          <t>880884</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>789039</t>
+          <t>781127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>892658</t>
+          <t>883053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1595066</t>
+          <t>1597860</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1735133</t>
+          <t>1738685</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1044488</t>
+          <t>1047086</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1151754</t>
+          <t>1159013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1010943</t>
+          <t>1004998</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1124122</t>
+          <t>1115388</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2085510</t>
+          <t>2087439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2240618</t>
+          <t>2249567</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>723319</t>
+          <t>724276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>822479</t>
+          <t>819670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>653481</t>
+          <t>659492</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>745058</t>
+          <t>754119</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1404719</t>
+          <t>1401141</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1543192</t>
+          <t>1546389</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>163522</t>
+          <t>163611</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>216897</t>
+          <t>216909</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>195564</t>
+          <t>197449</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>257350</t>
+          <t>258046</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>377541</t>
+          <t>377002</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>459907</t>
+          <t>460365</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>450556</t>
+          <t>448763</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>533829</t>
+          <t>532663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>653913</t>
+          <t>654897</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>753874</t>
+          <t>751347</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1129156</t>
+          <t>1137363</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1259303</t>
+          <t>1261267</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
